--- a/dialect_frontend/frontend/dialect/sinmin/tone.xlsx
+++ b/dialect_frontend/frontend/dialect/sinmin/tone.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84928BE-A48B-4BC6-99FD-6B3E8004C1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA02B92-0205-4B06-88CF-57CB78162F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6280" yWindow="4110" windowWidth="19200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>contour</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -111,6 +111,18 @@
   </si>
   <si>
     <t>ᴴᴴ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>¹³</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ᴸᴹ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -475,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="2"/>
@@ -521,19 +533,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="17">
-      <c r="A6" s="5" t="s">
-        <v>12</v>
+    <row r="6" spans="1:2">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="17">
       <c r="A7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
     </row>
@@ -545,10 +565,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D5EE90-4D8F-4AE0-9FCA-6B9979CDD301}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -556,7 +576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17">
+    <row r="2" spans="1:4" ht="17">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
@@ -567,7 +587,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="17">
+    <row r="3" spans="1:4" ht="17">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -578,7 +598,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="17">
+    <row r="4" spans="1:4" ht="17">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -589,7 +609,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -600,27 +620,42 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="17">
+      <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17">
-      <c r="A7" s="5" t="s">
+    <row r="8" spans="1:4" ht="17">
+      <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D8" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
